--- a/Dashboard.xlsx
+++ b/Dashboard.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8814408BB761E479/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adity\Desktop\Actuarial Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{BD227F34-8383-4064-84C6-0CB2BDFE5795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -200,7 +200,7 @@
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -406,20 +406,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="42">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -727,6 +713,38 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
@@ -846,24 +864,6 @@
     <dxf>
       <font>
         <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -1435,7 +1435,7 @@
                 <c:order val="1"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Data_Vehicle_Type!$C$2</c15:sqref>
@@ -1517,7 +1517,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Data_Vehicle_Type!$A$3:$A$7</c15:sqref>
@@ -1546,7 +1546,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Data_Vehicle_Type!$C$3:$C$7</c15:sqref>
@@ -1587,7 +1587,7 @@
                 <c:order val="2"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Data_Vehicle_Type!$D$2</c15:sqref>
@@ -1669,7 +1669,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Data_Vehicle_Type!$A$3:$A$7</c15:sqref>
@@ -1698,7 +1698,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Data_Vehicle_Type!$D$3:$D$7</c15:sqref>
@@ -1739,7 +1739,7 @@
                 <c:order val="3"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Data_Vehicle_Type!$E$2</c15:sqref>
@@ -1821,7 +1821,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Data_Vehicle_Type!$A$3:$A$7</c15:sqref>
@@ -1850,7 +1850,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Data_Vehicle_Type!$E$3:$E$7</c15:sqref>
@@ -1891,7 +1891,7 @@
                 <c:order val="4"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Data_Vehicle_Type!$F$2</c15:sqref>
@@ -1973,7 +1973,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Data_Vehicle_Type!$A$3:$A$7</c15:sqref>
@@ -2002,7 +2002,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Data_Vehicle_Type!$F$3:$F$7</c15:sqref>
@@ -2043,7 +2043,7 @@
                 <c:order val="5"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Data_Vehicle_Type!$G$2</c15:sqref>
@@ -2125,7 +2125,7 @@
                 </c:dLbls>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Data_Vehicle_Type!$A$3:$A$7</c15:sqref>
@@ -2154,7 +2154,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:extLst>
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>Data_Vehicle_Type!$G$3:$G$7</c15:sqref>
@@ -6916,8 +6916,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="137160" y="10146629"/>
-          <a:ext cx="10165079" cy="3136336"/>
+          <a:off x="143256" y="10327604"/>
+          <a:ext cx="10856975" cy="3194629"/>
           <a:chOff x="152400" y="10182824"/>
           <a:chExt cx="10393679" cy="3168721"/>
         </a:xfrm>
@@ -7891,14 +7891,14 @@
     <sortCondition descending="1" ref="H2:H7"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{D2FB8BAE-78E7-4905-8E96-0D39B471FF27}" name="vehicle_type" totalsRowLabel="Total" dataDxfId="28" totalsRowDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{7EDF69EE-4775-45FE-8B28-CB7D0C1090CB}" name="policies" totalsRowFunction="sum" dataDxfId="26" totalsRowDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{6D9936D1-EC8A-4699-9684-9AC35054CFCB}" name="claims" totalsRowFunction="sum" dataDxfId="24" totalsRowDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{0808AA99-1C41-4AAC-BC07-7471C3921265}" name="frequency" dataDxfId="22" totalsRowDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{F42B5BAB-5693-4D06-AF18-80233D5F477C}" name="avg_severity" dataDxfId="20" totalsRowDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{AA8B8274-1C5F-4CE6-90A6-363C36FB0129}" name="total_prem" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="19" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{F189719B-36D0-4B00-A682-A2F9E2C326A6}" name="total_loss" totalsRowFunction="sum" dataDxfId="16" totalsRowDxfId="17" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="8" xr3:uid="{7EFD0B50-F7B5-487D-9F5A-435E97C4F68E}" name="loss_ratio" dataDxfId="14" totalsRowDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{D2FB8BAE-78E7-4905-8E96-0D39B471FF27}" name="vehicle_type" totalsRowLabel="Total" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{7EDF69EE-4775-45FE-8B28-CB7D0C1090CB}" name="policies" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{6D9936D1-EC8A-4699-9684-9AC35054CFCB}" name="claims" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{0808AA99-1C41-4AAC-BC07-7471C3921265}" name="frequency" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{F42B5BAB-5693-4D06-AF18-80233D5F477C}" name="avg_severity" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{AA8B8274-1C5F-4CE6-90A6-363C36FB0129}" name="total_prem" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{F189719B-36D0-4B00-A682-A2F9E2C326A6}" name="total_loss" totalsRowFunction="sum" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
+    <tableColumn id="8" xr3:uid="{7EFD0B50-F7B5-487D-9F5A-435E97C4F68E}" name="loss_ratio" dataDxfId="15" totalsRowDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium17" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7911,12 +7911,12 @@
     <sortCondition ref="A2:A6"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6B974EC7-8C75-4321-A2FB-57594E3726FD}" name="age_groups" totalsRowLabel="Total" dataDxfId="10" totalsRowDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{68FA5F2F-8914-4907-90C3-5C211ABFE0F8}" name="policies" totalsRowFunction="sum" dataDxfId="8" totalsRowDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{9D7A7113-F87F-4EA4-A69B-182E20AEFEC7}" name="claims" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{53301379-C73B-4A11-8C3E-D8D69E2628F1}" name="frequency" dataDxfId="4" totalsRowDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{E88AAEA0-DAEB-4F24-A60A-03BF0C2CB45D}" name="severity" dataDxfId="2" totalsRowDxfId="3" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{F36B03EF-C354-4EE0-8C73-577DD26DA8CD}" name="loss_ratio" dataDxfId="0" totalsRowDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{6B974EC7-8C75-4321-A2FB-57594E3726FD}" name="age_groups" totalsRowLabel="Total" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{68FA5F2F-8914-4907-90C3-5C211ABFE0F8}" name="policies" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{9D7A7113-F87F-4EA4-A69B-182E20AEFEC7}" name="claims" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{53301379-C73B-4A11-8C3E-D8D69E2628F1}" name="frequency" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{E88AAEA0-DAEB-4F24-A60A-03BF0C2CB45D}" name="severity" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{F36B03EF-C354-4EE0-8C73-577DD26DA8CD}" name="loss_ratio" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium17" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8199,12 +8199,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F962F7A-2379-4E05-879A-8A9D9CBD264E}">
   <dimension ref="A1:D65"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="38.85546875" customWidth="1"/>
+    <col min="1" max="4" width="38.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="37.15" thickBot="1">
+    <row r="1" spans="1:4" ht="37.200000000000003" thickBot="1" x14ac:dyDescent="0.75">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -8212,7 +8212,7 @@
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
     </row>
-    <row r="2" spans="1:4" ht="32.450000000000003" thickTop="1" thickBot="1">
+    <row r="2" spans="1:4" ht="32.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -8220,7 +8220,7 @@
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
     </row>
-    <row r="3" spans="1:4" ht="18.600000000000001" thickBot="1">
+    <row r="3" spans="1:4" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -8234,7 +8234,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="43.9" customHeight="1" thickBot="1">
+    <row r="4" spans="1:4" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>10000</v>
       </c>
@@ -8248,7 +8248,7 @@
         <v>0.68130000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="32.450000000000003" thickTop="1" thickBot="1">
+    <row r="5" spans="1:4" ht="32.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A5" s="9" t="s">
         <v>6</v>
       </c>
@@ -8256,127 +8256,127 @@
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
     </row>
-    <row r="25" spans="1:4" ht="15" thickBot="1">
+    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
     </row>
-    <row r="26" spans="1:4" ht="32.450000000000003" thickTop="1" thickBot="1">
+    <row r="26" spans="1:4" ht="32.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A26" s="9" t="s">
         <v>7</v>
       </c>
@@ -8386,121 +8386,121 @@
       </c>
       <c r="D26" s="9"/>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
     </row>
-    <row r="45" spans="1:4" ht="15" thickBot="1">
+    <row r="45" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
     </row>
-    <row r="46" spans="1:4" ht="32.450000000000003" thickTop="1" thickBot="1">
+    <row r="46" spans="1:4" ht="32.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A46" s="9" t="s">
         <v>9</v>
       </c>
@@ -8508,115 +8508,115 @@
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -8636,19 +8636,20 @@
     <mergeCell ref="A26:B26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.9" thickBot="1">
+    <row r="1" spans="1:7" ht="31.8" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A1" s="13" t="s">
         <v>10</v>
       </c>
@@ -8659,7 +8660,7 @@
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
     </row>
-    <row r="2" spans="1:7" ht="15.6">
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -8682,7 +8683,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.6">
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>10000</v>
       </c>
@@ -8719,12 +8720,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56661936-2C29-485E-8652-C21666830C3D}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="8" width="16.28515625" customWidth="1"/>
+    <col min="1" max="8" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="31.9" thickBot="1">
+    <row r="1" spans="1:8" ht="31.8" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A1" s="13" t="s">
         <v>18</v>
       </c>
@@ -8736,7 +8737,7 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
     </row>
-    <row r="2" spans="1:8" ht="15.6">
+    <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -8762,7 +8763,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.6">
+    <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
@@ -8788,7 +8789,7 @@
         <v>0.84889999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.6">
+    <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
@@ -8814,7 +8815,7 @@
         <v>0.7661</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.6">
+    <row r="5" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
@@ -8840,7 +8841,7 @@
         <v>0.75349999999999995</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.6">
+    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
@@ -8866,7 +8867,7 @@
         <v>0.6623</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.6">
+    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
@@ -8892,7 +8893,7 @@
         <v>0.60899999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.6">
+    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
@@ -8930,12 +8931,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BF8720F-7418-4F1D-B0A7-D61B6D578A6B}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="19.7109375" customWidth="1"/>
+    <col min="1" max="6" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.9" thickBot="1">
+    <row r="1" spans="1:6" ht="31.8" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A1" s="13" t="s">
         <v>30</v>
       </c>
@@ -8945,7 +8946,7 @@
       <c r="E1" s="13"/>
       <c r="F1" s="13"/>
     </row>
-    <row r="2" spans="1:6" ht="15.6">
+    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
@@ -8965,7 +8966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.6">
+    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
@@ -8985,7 +8986,7 @@
         <v>0.62939999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.6">
+    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>34</v>
       </c>
@@ -9005,7 +9006,7 @@
         <v>0.67710000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.6">
+    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>35</v>
       </c>
@@ -9025,7 +9026,7 @@
         <v>0.68769999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.6">
+    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>36</v>
       </c>
@@ -9045,7 +9046,7 @@
         <v>0.71719999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.6">
+    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>29</v>
       </c>
@@ -9075,13 +9076,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BCC7065-4E9D-4E6C-BD51-C1B42801E4C6}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="25.42578125" customWidth="1"/>
+    <col min="1" max="4" width="25.44140625" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="31.9" thickBot="1">
+    <row r="1" spans="1:4" ht="31.8" thickBot="1" x14ac:dyDescent="0.65">
       <c r="A1" s="13" t="s">
         <v>8</v>
       </c>
@@ -9089,7 +9090,7 @@
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -9103,7 +9104,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -9117,7 +9118,7 @@
         <v>3752.11</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -9131,7 +9132,7 @@
         <v>4066.17</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -9145,7 +9146,7 @@
         <v>4345.67</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -9159,7 +9160,7 @@
         <v>3413.67</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -9173,7 +9174,7 @@
         <v>3631.17</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -9187,7 +9188,7 @@
         <v>4289.1099999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -9201,7 +9202,7 @@
         <v>4405.08</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -9215,7 +9216,7 @@
         <v>4071.62</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -9229,7 +9230,7 @@
         <v>4685.63</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -9243,7 +9244,7 @@
         <v>4759.46</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -9257,7 +9258,7 @@
         <v>3793.65</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -9271,7 +9272,7 @@
         <v>3871.48</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>29</v>
       </c>
